--- a/datafile/df_tsa_ly.xlsx
+++ b/datafile/df_tsa_ly.xlsx
@@ -2547,7 +2547,7 @@
         <v>2873682</v>
       </c>
       <c r="C192" t="n">
-        <v>43390</v>
+        <v>43389</v>
       </c>
     </row>
     <row r="193">
@@ -2580,7 +2580,7 @@
         <v>3007773</v>
       </c>
       <c r="C195" t="n">
-        <v>45278</v>
+        <v>45277</v>
       </c>
     </row>
     <row r="196">
@@ -2712,7 +2712,7 @@
         <v>2970569</v>
       </c>
       <c r="C207" t="n">
-        <v>46602</v>
+        <v>46601</v>
       </c>
     </row>
     <row r="208">
@@ -2767,7 +2767,7 @@
         <v>2574917</v>
       </c>
       <c r="C212" t="n">
-        <v>34654</v>
+        <v>34653</v>
       </c>
     </row>
     <row r="213">
@@ -3064,7 +3064,7 @@
         <v>1950994</v>
       </c>
       <c r="C239" t="n">
-        <v>25433</v>
+        <v>25430</v>
       </c>
     </row>
     <row r="240">
@@ -4285,7 +4285,7 @@
         <v>2503757</v>
       </c>
       <c r="C350" t="n">
-        <v>39367</v>
+        <v>39365</v>
       </c>
     </row>
     <row r="351">
@@ -4637,7 +4637,7 @@
         <v>2608430</v>
       </c>
       <c r="C382" t="n">
-        <v>34646</v>
+        <v>34645</v>
       </c>
     </row>
     <row r="383">
@@ -4659,7 +4659,7 @@
         <v>2231469</v>
       </c>
       <c r="C384" t="n">
-        <v>35387</v>
+        <v>35386</v>
       </c>
     </row>
     <row r="385">
@@ -4714,7 +4714,7 @@
         <v>2243481</v>
       </c>
       <c r="C389" t="n">
-        <v>30627</v>
+        <v>30625</v>
       </c>
     </row>
     <row r="390">
@@ -4747,7 +4747,7 @@
         <v>1830079</v>
       </c>
       <c r="C392" t="n">
-        <v>27147</v>
+        <v>27145</v>
       </c>
     </row>
     <row r="393">
@@ -5110,7 +5110,7 @@
         <v>2190541</v>
       </c>
       <c r="C425" t="n">
-        <v>30587</v>
+        <v>30586</v>
       </c>
     </row>
     <row r="426">
@@ -5407,7 +5407,7 @@
         <v>2744893</v>
       </c>
       <c r="C452" t="n">
-        <v>39185</v>
+        <v>39184</v>
       </c>
     </row>
     <row r="453">
@@ -5440,7 +5440,7 @@
         <v>2533621</v>
       </c>
       <c r="C455" t="n">
-        <v>38741</v>
+        <v>38740</v>
       </c>
     </row>
     <row r="456">
@@ -5924,7 +5924,7 @@
         <v>2399389</v>
       </c>
       <c r="C499" t="n">
-        <v>33060</v>
+        <v>33059</v>
       </c>
     </row>
     <row r="500">
@@ -5957,7 +5957,7 @@
         <v>2260950</v>
       </c>
       <c r="C502" t="n">
-        <v>36626</v>
+        <v>36624</v>
       </c>
     </row>
     <row r="503">
@@ -5979,7 +5979,7 @@
         <v>2782578</v>
       </c>
       <c r="C504" t="n">
-        <v>41132</v>
+        <v>41131</v>
       </c>
     </row>
     <row r="505">
@@ -5990,7 +5990,7 @@
         <v>2313392</v>
       </c>
       <c r="C505" t="n">
-        <v>34373</v>
+        <v>34372</v>
       </c>
     </row>
     <row r="506">
@@ -6023,7 +6023,7 @@
         <v>2976209</v>
       </c>
       <c r="C508" t="n">
-        <v>48788</v>
+        <v>48790</v>
       </c>
     </row>
     <row r="509">
@@ -6034,7 +6034,7 @@
         <v>2380377</v>
       </c>
       <c r="C509" t="n">
-        <v>40398</v>
+        <v>40397</v>
       </c>
     </row>
     <row r="510">
@@ -6078,7 +6078,7 @@
         <v>2374930</v>
       </c>
       <c r="C513" t="n">
-        <v>38365</v>
+        <v>38364</v>
       </c>
     </row>
     <row r="514">
@@ -6210,7 +6210,7 @@
         <v>2764691</v>
       </c>
       <c r="C525" t="n">
-        <v>41657</v>
+        <v>41656</v>
       </c>
     </row>
     <row r="526">
@@ -6221,7 +6221,7 @@
         <v>2360445</v>
       </c>
       <c r="C526" t="n">
-        <v>35618</v>
+        <v>35617</v>
       </c>
     </row>
     <row r="527">
@@ -6232,7 +6232,7 @@
         <v>2517148</v>
       </c>
       <c r="C527" t="n">
-        <v>36455</v>
+        <v>36450</v>
       </c>
     </row>
     <row r="528">
@@ -6254,7 +6254,7 @@
         <v>2873210</v>
       </c>
       <c r="C529" t="n">
-        <v>44884</v>
+        <v>44883</v>
       </c>
     </row>
     <row r="530">
@@ -6265,7 +6265,7 @@
         <v>2534457</v>
       </c>
       <c r="C530" t="n">
-        <v>39365</v>
+        <v>39361</v>
       </c>
     </row>
     <row r="531">
@@ -6276,7 +6276,7 @@
         <v>2891326</v>
       </c>
       <c r="C531" t="n">
-        <v>44652</v>
+        <v>44649</v>
       </c>
     </row>
     <row r="532">
@@ -6287,7 +6287,7 @@
         <v>2849377</v>
       </c>
       <c r="C532" t="n">
-        <v>44283</v>
+        <v>44282</v>
       </c>
     </row>
     <row r="533">
@@ -6298,7 +6298,7 @@
         <v>2482257</v>
       </c>
       <c r="C533" t="n">
-        <v>37981</v>
+        <v>37976</v>
       </c>
     </row>
     <row r="534">
@@ -6309,7 +6309,7 @@
         <v>2638190</v>
       </c>
       <c r="C534" t="n">
-        <v>40496</v>
+        <v>40494</v>
       </c>
     </row>
     <row r="535">
@@ -6320,7 +6320,7 @@
         <v>2988204</v>
       </c>
       <c r="C535" t="n">
-        <v>43843</v>
+        <v>43835</v>
       </c>
     </row>
     <row r="536">
@@ -6331,7 +6331,7 @@
         <v>2881272</v>
       </c>
       <c r="C536" t="n">
-        <v>47528</v>
+        <v>47521</v>
       </c>
     </row>
     <row r="537">
@@ -6342,7 +6342,7 @@
         <v>2563971</v>
       </c>
       <c r="C537" t="n">
-        <v>41243</v>
+        <v>41239</v>
       </c>
     </row>
     <row r="538">
@@ -6353,7 +6353,7 @@
         <v>2981485</v>
       </c>
       <c r="C538" t="n">
-        <v>45908</v>
+        <v>45907</v>
       </c>
     </row>
     <row r="539">
@@ -6364,7 +6364,7 @@
         <v>2876770</v>
       </c>
       <c r="C539" t="n">
-        <v>45910</v>
+        <v>45907</v>
       </c>
     </row>
     <row r="540">
@@ -6375,7 +6375,7 @@
         <v>2571215</v>
       </c>
       <c r="C540" t="n">
-        <v>39479</v>
+        <v>39477</v>
       </c>
     </row>
     <row r="541">
@@ -6386,7 +6386,7 @@
         <v>2656150</v>
       </c>
       <c r="C541" t="n">
-        <v>39903</v>
+        <v>39902</v>
       </c>
     </row>
     <row r="542">
@@ -6397,7 +6397,7 @@
         <v>2910453</v>
       </c>
       <c r="C542" t="n">
-        <v>43741</v>
+        <v>43740</v>
       </c>
     </row>
     <row r="543">
@@ -6408,7 +6408,7 @@
         <v>2904610</v>
       </c>
       <c r="C543" t="n">
-        <v>45763</v>
+        <v>45767</v>
       </c>
     </row>
     <row r="544">
@@ -6419,7 +6419,7 @@
         <v>2575625</v>
       </c>
       <c r="C544" t="n">
-        <v>40858</v>
+        <v>40857</v>
       </c>
     </row>
     <row r="545">
@@ -6430,7 +6430,7 @@
         <v>2930672</v>
       </c>
       <c r="C545" t="n">
-        <v>46027</v>
+        <v>46026</v>
       </c>
     </row>
     <row r="546">
@@ -6441,7 +6441,7 @@
         <v>2690919</v>
       </c>
       <c r="C546" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="547">
@@ -6452,7 +6452,7 @@
         <v>2477905</v>
       </c>
       <c r="C547" t="n">
-        <v>43102</v>
+        <v>43095</v>
       </c>
     </row>
     <row r="548">
@@ -6463,7 +6463,7 @@
         <v>2654017</v>
       </c>
       <c r="C548" t="n">
-        <v>43583</v>
+        <v>43578</v>
       </c>
     </row>
     <row r="549">
@@ -6474,7 +6474,7 @@
         <v>2901753</v>
       </c>
       <c r="C549" t="n">
-        <v>48729</v>
+        <v>48724</v>
       </c>
     </row>
     <row r="550">
@@ -6485,7 +6485,7 @@
         <v>2572397</v>
       </c>
       <c r="C550" t="n">
-        <v>50709</v>
+        <v>50687</v>
       </c>
     </row>
     <row r="551">
